--- a/samples/checked/daily/2605/incoming-a/クレーム集計260501.xlsx
+++ b/samples/checked/daily/2605/incoming-a/クレーム集計260501.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日次集計" sheetId="1" r:id="Re80e3a3cee32499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日次集計" sheetId="1" r:id="Re8afeb703bff4840"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -264,11 +264,11 @@
   <x:cols>
     <x:col min="1" max="1" width="7.25" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="8.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12.25" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="8.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.5" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="5.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="3.880000114440918" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -302,19 +302,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="E2" s="3" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="F2" s="3" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G2" s="3" t="str">
-        <x:v>normal</x:v>
+        <x:v>正常</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -325,19 +325,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C3" s="3" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="D3" s="3" t="str">
         <x:v>REP</x:v>
       </x:c>
       <x:c r="E3" s="3" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
       <x:c r="F3" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G3" s="3" t="str">
-        <x:v>normal</x:v>
+        <x:v>正常</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -348,19 +348,19 @@
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="C4" s="3" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="D4" s="3" t="str">
         <x:v>APP</x:v>
       </x:c>
       <x:c r="E4" s="3" t="str">
-        <x:v>App Support</x:v>
+        <x:v>アプリ支援</x:v>
       </x:c>
       <x:c r="F4" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G4" s="3" t="str">
-        <x:v>normal</x:v>
+        <x:v>正常</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -371,19 +371,19 @@
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="C5" s="3" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="D5" s="3" t="str">
         <x:v>CON</x:v>
       </x:c>
       <x:c r="E5" s="3" t="str">
-        <x:v>Contract Desk</x:v>
+        <x:v>契約確認</x:v>
       </x:c>
       <x:c r="F5" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G5" s="3" t="str">
-        <x:v>normal</x:v>
+        <x:v>正常</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
